--- a/output/pdf_financials_xlsx/AWE.xlsx
+++ b/output/pdf_financials_xlsx/AWE.xlsx
@@ -5265,40 +5265,40 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.031347</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.079915</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.100861</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.215846</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.378497</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.517568</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.594572</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.938527</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.267901</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.36732</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.443239</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.518288</v>
       </c>
     </row>
     <row r="93">
@@ -6528,37 +6528,37 @@
         <v>0</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.13256</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0</v>
+        <v>-0.098094</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-0.266841</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.239926</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0</v>
+        <v>-0.533765</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.940186</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-1.010959</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-1.147162</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.287096</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-0.09615700000000001</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.270108</v>
       </c>
     </row>
     <row r="119">
@@ -8490,7 +8490,11 @@
           <t>Reserves (note 5(e))</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -9176,7 +9180,11 @@
           <t>Reserves (note 6(e))</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -11138,7 +11146,11 @@
           <t>Reserves (note 5(d))</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -11724,7 +11736,11 @@
           <t>Reserve (note 4(d))</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -12056,7 +12072,11 @@
           <t>Reserve (note 4(e))</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -12392,7 +12412,11 @@
           <t>Reserve (note 4 (e))</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -13266,7 +13290,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -17196,7 +17224,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/AWE.xlsx
+++ b/output/pdf_financials_xlsx/AWE.xlsx
@@ -844,10 +844,10 @@
         <v>0.00017</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.000328</v>
+        <v>0.097636</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.040851</v>
+        <v>0.134123</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0.12277</v>
@@ -893,7 +893,7 @@
         <v>-0.00017</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.000328</v>
+        <v>-0.097636</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>-0.134123</v>
@@ -2109,40 +2109,40 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.429335</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.26419</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.061594</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.244398</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.224169</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.03695</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.025543</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.057556</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.31377</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.011516</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.014215</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.483005</v>
       </c>
     </row>
     <row r="35">
@@ -2215,40 +2215,40 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.429335</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.26419</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.061594</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.244398</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.224169</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.03695</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.025543</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.057556</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.31377</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.011516</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.014215</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.483005</v>
       </c>
     </row>
     <row r="37">
@@ -2854,37 +2854,37 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.270703</v>
+        <v>0.006513</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.113126</v>
+        <v>0.051532</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.273321</v>
+        <v>0.028923</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.27832</v>
+        <v>0.054151</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.07216</v>
+        <v>0.03521</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.049034</v>
+        <v>0.023491</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.090642</v>
+        <v>0.033086</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.343903</v>
+        <v>0.030133</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.01309</v>
+        <v>0.001574</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.015789</v>
+        <v>0.001574</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.484579</v>
+        <v>0.001574</v>
       </c>
     </row>
     <row r="49">
@@ -6837,13 +6837,13 @@
         <v>0</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.022113</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.095664</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.062297</v>
       </c>
       <c r="M124" s="3" t="n">
         <v>0</v>
@@ -6886,13 +6886,13 @@
         <v>0</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.022113</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.095664</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.062297</v>
       </c>
       <c r="M125" s="3" t="n">
         <v>0</v>
@@ -7556,7 +7556,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9858,7 +9858,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -14826,7 +14826,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E91" t="inlineStr">
         <is>
           <t>-</t>
@@ -30896,7 +30900,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -30905,10 +30909,10 @@
         </is>
       </c>
       <c r="F278" s="5" t="n">
-        <v>-0.097636</v>
+        <v>0.097636</v>
       </c>
       <c r="G278" s="5" t="n">
-        <v>-0.134123</v>
+        <v>0.134123</v>
       </c>
       <c r="H278" t="inlineStr">
         <is>
